--- a/what.xlsx
+++ b/what.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aiden\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d14bd4a04985854/Documents/GitHub/AIAA-Systems-Engineering-Workshop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87A94B5A-B463-4E97-B5D1-C35B1CC20F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="8_{87A94B5A-B463-4E97-B5D1-C35B1CC20F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C0AA74-77B2-48C6-A342-A92AFF607D6D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2636F9F0-5E7E-44FC-9830-686971031DD6}"/>
   </bookViews>
@@ -33,6 +33,65 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> System of System</t>
+  </si>
+  <si>
+    <t>Subsystem</t>
+  </si>
+  <si>
+    <t>Element</t>
+  </si>
+  <si>
+    <t>Plane</t>
+  </si>
+  <si>
+    <t>Whole Plane</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>Airframe</t>
+  </si>
+  <si>
+    <t>Propulsion</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Electrical</t>
+  </si>
+  <si>
+    <t>Fuselage</t>
+  </si>
+  <si>
+    <t>Wings</t>
+  </si>
+  <si>
+    <t>Tail</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Propeller</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>Battery</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +461,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF071673-76A8-430C-97C2-4609D76DC331}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="17.54296875" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/what.xlsx
+++ b/what.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4d14bd4a04985854/Documents/GitHub/AIAA-Systems-Engineering-Workshop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{87A94B5A-B463-4E97-B5D1-C35B1CC20F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C0AA74-77B2-48C6-A342-A92AFF607D6D}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{87A94B5A-B463-4E97-B5D1-C35B1CC20F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0810844B-83EB-41FF-B3C6-A3BB60BE626A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2636F9F0-5E7E-44FC-9830-686971031DD6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>System</t>
   </si>
@@ -90,6 +90,24 @@
   </si>
   <si>
     <t>Battery</t>
+  </si>
+  <si>
+    <t>Reciever</t>
+  </si>
+  <si>
+    <t>Ailerons</t>
+  </si>
+  <si>
+    <t>Rudder</t>
+  </si>
+  <si>
+    <t>Elevators</t>
+  </si>
+  <si>
+    <t>Pilot</t>
+  </si>
+  <si>
+    <t>Transmitter</t>
   </si>
 </sst>
 </file>
@@ -142,6 +160,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -461,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF071673-76A8-430C-97C2-4609D76DC331}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
@@ -533,24 +555,54 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C15" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D15" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B17" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
